--- a/reports/2026-03-16.xlsx
+++ b/reports/2026-03-16.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AG$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AG$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-16 05:57 UTC</t>
+          <t>2026-03-16 15:32 UTC</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -642,7 +642,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-16_1773640527164</t>
+          <t>2026-03-16_1773675009352</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NEOUSDT</t>
+          <t>CAKEUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>75.288</v>
+        <v>75.904</v>
       </c>
       <c r="I2" t="n">
-        <v>94.11</v>
+        <v>94.88</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -941,25 +941,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.645300510556884</v>
+        <v>1.377583526080592</v>
       </c>
       <c r="P2" t="n">
-        <v>2.848</v>
+        <v>1.502</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.662626179301046</v>
+        <v>9.031501289318467</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>2.419</v>
+        <v>1.169</v>
       </c>
       <c r="T2" t="n">
-        <v>8.55481294672429</v>
+        <v>15.14126164632936</v>
       </c>
       <c r="U2" t="n">
-        <v>2.871601021113768</v>
+        <v>1.586167052161185</v>
       </c>
       <c r="V2" t="n">
-        <v>3.097901531670652</v>
+        <v>1.794750578241777</v>
       </c>
       <c r="W2" t="n">
-        <v>3.324202042227536</v>
+        <v>2.00333410432237</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -988,22 +988,22 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03509387611861343</v>
+        <v>0.06655574043260498</v>
       </c>
       <c r="AA2" t="n">
-        <v>12338.509143</v>
+        <v>129519.55706</v>
       </c>
       <c r="AB2" t="n">
-        <v>13356.687751</v>
+        <v>101197.76054</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.643408</v>
+        <v>4.305977</v>
       </c>
       <c r="AD2" t="n">
-        <v>79.62982700000001</v>
+        <v>10.721407</v>
       </c>
       <c r="AE2" t="n">
-        <v>200342902.5119538</v>
+        <v>494925978.2526067</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUSDT</t>
+          <t>NEOUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1047,19 +1047,15 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.488</v>
+        <v>75.288</v>
       </c>
       <c r="I3" t="n">
-        <v>81.86</v>
+        <v>94.11</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>none</t>
@@ -1074,13 +1070,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04251637342558565</v>
+        <v>2.645300510556884</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04894</v>
+        <v>2.789</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.10859477621558</v>
+        <v>5.432255763367499</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1088,19 +1084,19 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.03667</v>
+        <v>2.419</v>
       </c>
       <c r="T3" t="n">
-        <v>13.7508751441801</v>
+        <v>8.55481294672429</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04836274685117131</v>
+        <v>2.871601021113768</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05420912027675696</v>
+        <v>3.097901531670652</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06005549370234261</v>
+        <v>3.324202042227536</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -1109,22 +1105,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02039775624680494</v>
+        <v>0.07165890361876674</v>
       </c>
       <c r="AA3" t="n">
-        <v>14639.4710375</v>
+        <v>12512.478873</v>
       </c>
       <c r="AB3" t="n">
-        <v>16992.6016453</v>
+        <v>11025.137397</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.539845</v>
+        <v>17.784624</v>
       </c>
       <c r="AD3" t="n">
-        <v>44.599143</v>
+        <v>99.703883</v>
       </c>
       <c r="AE3" t="n">
-        <v>141556508.4303511</v>
+        <v>196330253.5828413</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -1139,12 +1135,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EIGENUSDT</t>
+          <t>BBUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EigenCloud</t>
+          <t>BounceBit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1154,7 +1150,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1168,10 +1164,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>65.47199999999999</v>
+        <v>67.592</v>
       </c>
       <c r="I4" t="n">
-        <v>81.84</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1183,25 +1179,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1935899444960997</v>
+        <v>0.02790929470802848</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2196</v>
+        <v>0.02884</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.43564386652545</v>
+        <v>3.334750310633217</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1209,43 +1205,43 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.1696</v>
+        <v>0.0235</v>
       </c>
       <c r="T4" t="n">
-        <v>12.39214389907687</v>
+        <v>15.79866046116919</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2175798889921995</v>
+        <v>0.03231858941605696</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2415698334882992</v>
+        <v>0.03672788412408544</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2655597779843989</v>
+        <v>0.04113717883211392</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09103322712790429</v>
+        <v>0.1731601731601661</v>
       </c>
       <c r="AA4" t="n">
-        <v>81765.935514</v>
+        <v>518.2395081999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>53725.338742</v>
+        <v>10856.6918679</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.599563</v>
+        <v>12.120301</v>
       </c>
       <c r="AD4" t="n">
-        <v>33.968546</v>
+        <v>126.795303</v>
       </c>
       <c r="AE4" t="n">
-        <v>141862203.1409119</v>
+        <v>30100401.45894412</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1260,12 +1256,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ONTUSDT</t>
+          <t>SUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1289,10 +1285,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>61.512</v>
+        <v>65.488</v>
       </c>
       <c r="I5" t="n">
-        <v>76.89</v>
+        <v>81.86</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1316,13 +1312,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04230336070690488</v>
+        <v>0.04251637342558565</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0436</v>
+        <v>0.04999</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.065097598459787</v>
+        <v>17.57823156646949</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1330,19 +1326,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.03883</v>
+        <v>0.03667</v>
       </c>
       <c r="T5" t="n">
-        <v>8.210602299353358</v>
+        <v>13.7508751441801</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04577672141380976</v>
+        <v>0.04836274685117131</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04925008212071463</v>
+        <v>0.05420912027675696</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05272344282761951</v>
+        <v>0.06005549370234261</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1351,22 +1347,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1375200550080164</v>
+        <v>0.01999800019997225</v>
       </c>
       <c r="AA5" t="n">
-        <v>4756.5967106</v>
+        <v>15857.7854915</v>
       </c>
       <c r="AB5" t="n">
-        <v>3056.9484425</v>
+        <v>12320.2825642</v>
       </c>
       <c r="AC5" t="n">
-        <v>81.090335</v>
+        <v>15.202372</v>
       </c>
       <c r="AD5" t="n">
-        <v>8743.020782</v>
+        <v>284.805279</v>
       </c>
       <c r="AE5" t="n">
-        <v>40774760.97905913</v>
+        <v>143834978.4251222</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1381,12 +1377,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REZUSDT</t>
+          <t>EIGENUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Renzo</t>
+          <t>EigenCloud</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1396,50 +1392,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.2</v>
+        <v>65.47199999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>68</v>
+        <v>81.84</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003521820873396659</v>
+        <v>0.1935899444960997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.004027</v>
+        <v>0.2152</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.34425953969984</v>
+        <v>11.16279854315245</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.00334433672338398</v>
+        <v>0.1696</v>
       </c>
       <c r="T6" t="n">
-        <v>5.039556422456634</v>
+        <v>12.39214389907687</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003699305023409339</v>
+        <v>0.2175798889921995</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003876789173422019</v>
+        <v>0.2415698334882992</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004054273323434698</v>
+        <v>0.2655597779843989</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1468,22 +1468,22 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.198461920119082</v>
+        <v>0.09280742459397016</v>
       </c>
       <c r="AA6" t="n">
-        <v>10157.08912587</v>
+        <v>58986.53928599999</v>
       </c>
       <c r="AB6" t="n">
-        <v>2226.29849701</v>
+        <v>56898.246609</v>
       </c>
       <c r="AC6" t="n">
-        <v>82.28304300000001</v>
+        <v>21.230981</v>
       </c>
       <c r="AD6" t="n">
-        <v>190.330867</v>
+        <v>22.835401</v>
       </c>
       <c r="AE6" t="n">
-        <v>28484778.8716311</v>
+        <v>139189718.4834139</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZENUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Horizen</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>59.168</v>
+        <v>61.016</v>
       </c>
       <c r="I7" t="n">
-        <v>73.95999999999999</v>
+        <v>76.27</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.653305171976704</v>
+        <v>6.061063817434262e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.248</v>
+        <v>6.517e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.5194184628699</v>
+        <v>7.522378847988143</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1568,43 +1568,43 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4.94</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>12.61748924350555</v>
+        <v>15.27889897431039</v>
       </c>
       <c r="U7" t="n">
-        <v>6.366610343953407</v>
+        <v>6.987127634868524e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.07991551593011</v>
+        <v>7.913191452302786e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.793220687906813</v>
+        <v>8.839255269737048e-06</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04799616030717724</v>
+        <v>0.1532332209623032</v>
       </c>
       <c r="AA7" t="n">
-        <v>14692.91218</v>
+        <v>189815.638465952</v>
       </c>
       <c r="AB7" t="n">
-        <v>14193.57388</v>
+        <v>211253.737924424</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.417535</v>
+        <v>7.661661</v>
       </c>
       <c r="AD7" t="n">
-        <v>107.110515</v>
+        <v>7.661661</v>
       </c>
       <c r="AE7" t="n">
-        <v>111479311.0662243</v>
+        <v>574448583.7315314</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RENDERUSDT</t>
+          <t>ETCUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1634,29 +1634,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>55.44</v>
+        <v>59.976</v>
       </c>
       <c r="I8" t="n">
-        <v>61.6</v>
+        <v>74.97</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>direct</t>
@@ -1671,13 +1675,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.794923351021833</v>
+        <v>8.460252391107007</v>
       </c>
       <c r="P8" t="n">
-        <v>1.884</v>
+        <v>8.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.962699322366948</v>
+        <v>5.552406561614731</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1685,43 +1689,43 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1.658853690195508</v>
+        <v>7.14</v>
       </c>
       <c r="T8" t="n">
-        <v>7.580806208179395</v>
+        <v>15.60535466406168</v>
       </c>
       <c r="U8" t="n">
-        <v>1.930993011848158</v>
+        <v>9.780504782214013</v>
       </c>
       <c r="V8" t="n">
-        <v>2.067062672674483</v>
+        <v>11.10075717332102</v>
       </c>
       <c r="W8" t="n">
-        <v>2.203132333500808</v>
+        <v>12.42100956442803</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05303632988596605</v>
+        <v>0.1119194180190239</v>
       </c>
       <c r="AA8" t="n">
-        <v>147861.81799</v>
+        <v>88378.84323</v>
       </c>
       <c r="AB8" t="n">
-        <v>153210.54343</v>
+        <v>55029.01777</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.80983</v>
+        <v>5.595971</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.509838</v>
+        <v>10.748068</v>
       </c>
       <c r="AE8" t="n">
-        <v>976872435.750208</v>
+        <v>1391286098.117296</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1736,22 +1740,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CAKEUSDT</t>
+          <t>KASUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1765,36 +1769,40 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>75.904</v>
+        <v>59.392</v>
       </c>
       <c r="I9" t="n">
-        <v>94.88</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.377583526080592</v>
+        <v>0.03061209080528285</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>0.03369</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.78995471741042</v>
+        <v>10.05455398095834</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1802,43 +1810,43 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1.169</v>
+        <v>0.025188</v>
       </c>
       <c r="T9" t="n">
-        <v>15.14126164632936</v>
+        <v>17.71878582153819</v>
       </c>
       <c r="U9" t="n">
-        <v>1.586167052161185</v>
+        <v>0.03603618161056571</v>
       </c>
       <c r="V9" t="n">
-        <v>1.794750578241777</v>
+        <v>0.04146027241584856</v>
       </c>
       <c r="W9" t="n">
-        <v>2.00333410432237</v>
+        <v>0.04688436322113142</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.06491398896461473</v>
+        <v>0.08301707779886221</v>
       </c>
       <c r="AA9" t="n">
-        <v>152592.46014</v>
+        <v>52430.40961702</v>
       </c>
       <c r="AB9" t="n">
-        <v>148962.56459</v>
+        <v>34047.04133134</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.581866</v>
+        <v>7.503122</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.385214</v>
+        <v>20.501842</v>
       </c>
       <c r="AE9" t="n">
-        <v>508358098.9013084</v>
+        <v>917032545.5770435</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1853,22 +1861,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CFXUSDT</t>
+          <t>ZENUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Conflux</t>
+          <t>Horizen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1882,15 +1890,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72.688</v>
+        <v>59.168</v>
       </c>
       <c r="I10" t="n">
-        <v>90.86</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -1902,16 +1914,16 @@
         </is>
       </c>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05237198864706193</v>
+        <v>5.653305171976704</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06351</v>
+        <v>6.214</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.26711557202423</v>
+        <v>9.918000372643032</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1919,19 +1931,19 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.04031</v>
+        <v>4.94</v>
       </c>
       <c r="T10" t="n">
-        <v>23.03137413465128</v>
+        <v>12.61748924350555</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06443397729412385</v>
+        <v>6.366610343953407</v>
       </c>
       <c r="V10" t="n">
-        <v>0.07649596594118578</v>
+        <v>7.07991551593011</v>
       </c>
       <c r="W10" t="n">
-        <v>0.08855795458824771</v>
+        <v>7.793220687906813</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1940,22 +1952,22 @@
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0157517523824683</v>
+        <v>0.03218020917135607</v>
       </c>
       <c r="AA10" t="n">
-        <v>37416.3096725</v>
+        <v>14449.31822</v>
       </c>
       <c r="AB10" t="n">
-        <v>25505.3997432</v>
+        <v>12521.60339</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.559081</v>
+        <v>9.525416999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>22.414103</v>
+        <v>105.23279</v>
       </c>
       <c r="AE10" t="n">
-        <v>329328159.3566397</v>
+        <v>111086132.4720163</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1970,39 +1982,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>QUBICUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Qubic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>70.752</v>
+        <v>58.32</v>
       </c>
       <c r="I11" t="n">
-        <v>88.44</v>
+        <v>64.8</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2010,25 +2022,25 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>9.415545255142318</v>
+        <v>9.010145353508996e-07</v>
       </c>
       <c r="P11" t="n">
-        <v>10.473</v>
+        <v>1.0371e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.23094538024925</v>
+        <v>15.10358149728428</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2036,43 +2048,43 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>7.55</v>
+        <v>8.043787136442057e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>19.81345959888459</v>
+        <v>10.72522339154709</v>
       </c>
       <c r="U11" t="n">
-        <v>11.28109051028463</v>
+        <v>9.976503570575936e-07</v>
       </c>
       <c r="V11" t="n">
-        <v>13.14663576542695</v>
+        <v>1.094286178764287e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>15.01218102056927</v>
+        <v>1.190922000470982e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9999999999999996</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009540619186179895</v>
+        <v>0.211905220574066</v>
       </c>
       <c r="AA11" t="n">
-        <v>613464.11677</v>
+        <v>2460.5571155293</v>
       </c>
       <c r="AB11" t="n">
-        <v>568863.86384</v>
+        <v>3172.491420091</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.775899</v>
+        <v>107.98297</v>
       </c>
       <c r="AD11" t="n">
-        <v>8.235046000000001</v>
+        <v>505.602041</v>
       </c>
       <c r="AE11" t="n">
-        <v>4514679963.492872</v>
+        <v>140670440.2592961</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2087,39 +2099,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FETUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence Alliance</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68.992</v>
+        <v>58.32</v>
       </c>
       <c r="I12" t="n">
-        <v>86.23999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2136,16 +2148,16 @@
         </is>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1647434377664609</v>
+        <v>256.7971756600807</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2036</v>
+        <v>290</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.58610622695747</v>
+        <v>12.9295909328339</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2153,19 +2165,19 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.1339</v>
+        <v>230.3411380137109</v>
       </c>
       <c r="T12" t="n">
-        <v>18.72210400889192</v>
+        <v>10.3023086520972</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1955868755329219</v>
+        <v>283.2532133064504</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2264303132993828</v>
+        <v>309.7092509528201</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2572737510658438</v>
+        <v>336.1652885991899</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2174,22 +2186,22 @@
         <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.04910385465258482</v>
+        <v>0.04821932906249335</v>
       </c>
       <c r="AA12" t="n">
-        <v>54741.837359</v>
+        <v>166264.25511</v>
       </c>
       <c r="AB12" t="n">
-        <v>63677.083364</v>
+        <v>183500.17237</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.99948</v>
+        <v>2.410966</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.738461</v>
+        <v>3.392047</v>
       </c>
       <c r="AE12" t="n">
-        <v>458705983.4103365</v>
+        <v>3121809476.65737</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2204,22 +2216,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QTUMUSDT</t>
+          <t>FARTCOINUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qtum</t>
+          <t>Fartcoin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2233,10 +2245,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67.744</v>
+        <v>58.032</v>
       </c>
       <c r="I13" t="n">
-        <v>84.68000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -2257,16 +2269,16 @@
         </is>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9112573762139879</v>
+        <v>0.1634675277966182</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9486</v>
+        <v>0.18023</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.097922799940434</v>
+        <v>10.2543131527854</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2274,19 +2286,19 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.77</v>
+        <v>0.13836</v>
       </c>
       <c r="T13" t="n">
-        <v>15.5013698545708</v>
+        <v>15.35933658203746</v>
       </c>
       <c r="U13" t="n">
-        <v>1.052514752427976</v>
+        <v>0.1885750555932365</v>
       </c>
       <c r="V13" t="n">
-        <v>1.193772128641964</v>
+        <v>0.2136825833898547</v>
       </c>
       <c r="W13" t="n">
-        <v>1.335029504855952</v>
+        <v>0.2387901111864729</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
@@ -2295,22 +2307,22 @@
         <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.09487165972698169</v>
+        <v>0.1883552157775231</v>
       </c>
       <c r="AA13" t="n">
-        <v>7261.325366</v>
+        <v>8207.1954768</v>
       </c>
       <c r="AB13" t="n">
-        <v>7343.578281</v>
+        <v>7865.687407400001</v>
       </c>
       <c r="AC13" t="n">
-        <v>33.065142</v>
+        <v>38.02951</v>
       </c>
       <c r="AD13" t="n">
-        <v>2558.47854</v>
+        <v>305.197508</v>
       </c>
       <c r="AE13" t="n">
-        <v>100418212.9328517</v>
+        <v>179907225.1536074</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2325,22 +2337,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QNTUSDT</t>
+          <t>ORDIUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>ORDI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NO_TRADE</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2354,10 +2366,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>66.928</v>
+        <v>57.648</v>
       </c>
       <c r="I14" t="n">
-        <v>83.66</v>
+        <v>72.06</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2369,25 +2381,25 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>65.0063783597205</v>
+        <v>2.527602926075091</v>
       </c>
       <c r="P14" t="n">
-        <v>68.2</v>
+        <v>2.703</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.91278197749645</v>
+        <v>6.939265345655743</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2395,19 +2407,19 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>53.58</v>
+        <v>2.181</v>
       </c>
       <c r="T14" t="n">
-        <v>17.57731879245954</v>
+        <v>13.71271264562517</v>
       </c>
       <c r="U14" t="n">
-        <v>76.432756719441</v>
+        <v>2.874205852150181</v>
       </c>
       <c r="V14" t="n">
-        <v>87.8591350791615</v>
+        <v>3.220808778225272</v>
       </c>
       <c r="W14" t="n">
-        <v>99.28551343888201</v>
+        <v>3.567411704300363</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -2416,22 +2428,22 @@
         <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1026317718642228</v>
+        <v>0.07396449704142841</v>
       </c>
       <c r="AA14" t="n">
-        <v>6423.5705</v>
+        <v>49739.07573</v>
       </c>
       <c r="AB14" t="n">
-        <v>4827.7669</v>
+        <v>48814.61005</v>
       </c>
       <c r="AC14" t="n">
-        <v>36.781854</v>
+        <v>9.821902</v>
       </c>
       <c r="AD14" t="n">
-        <v>1921.210915</v>
+        <v>16.473303</v>
       </c>
       <c r="AE14" t="n">
-        <v>823059487.509383</v>
+        <v>56859550.32031852</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2446,12 +2458,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1INCHUSDT</t>
+          <t>CFXUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1inch</t>
+          <t>Conflux</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2461,7 +2473,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2475,19 +2487,15 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.288</v>
+        <v>72.688</v>
       </c>
       <c r="I15" t="n">
-        <v>76.61</v>
+        <v>90.86</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>none</t>
@@ -2502,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09586862404073367</v>
+        <v>0.05237198864706193</v>
       </c>
       <c r="P15" t="n">
-        <v>0.10218</v>
+        <v>0.0649</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.583359281953083</v>
+        <v>23.92120611910522</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2516,43 +2524,43 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.08</v>
+        <v>0.04031</v>
       </c>
       <c r="T15" t="n">
-        <v>16.5524687555662</v>
+        <v>23.03137413465128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1117372480814673</v>
+        <v>0.06443397729412385</v>
       </c>
       <c r="V15" t="n">
-        <v>0.127605872122201</v>
+        <v>0.07649596594118578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1434744961629347</v>
+        <v>0.08855795458824771</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.999999999999999</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1564792176039192</v>
+        <v>0.01543805480511</v>
       </c>
       <c r="AA15" t="n">
-        <v>9186.399368099999</v>
+        <v>25791.0993088</v>
       </c>
       <c r="AB15" t="n">
-        <v>6497.9509368</v>
+        <v>32267.5050568</v>
       </c>
       <c r="AC15" t="n">
-        <v>42.484517</v>
+        <v>6.627583</v>
       </c>
       <c r="AD15" t="n">
-        <v>1773.974485</v>
+        <v>17.496857</v>
       </c>
       <c r="AE15" t="n">
-        <v>143392938.3627453</v>
+        <v>337155751.9256588</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2567,12 +2575,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XVSUSDT</t>
+          <t>FETUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Artificial Superintelligence Alliance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2582,7 +2590,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>price_past_target_1 | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2596,40 +2604,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>58.72</v>
+        <v>68.992</v>
       </c>
       <c r="I16" t="n">
-        <v>73.40000000000001</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.014494227100955</v>
+        <v>0.1647434377664609</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1711</v>
+        <v>0.2291</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.195092811627422</v>
+        <v>39.06471972787797</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2637,19 +2641,19 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>2.5006</v>
+        <v>0.1339</v>
       </c>
       <c r="T16" t="n">
-        <v>17.0474443931899</v>
+        <v>18.72210400889192</v>
       </c>
       <c r="U16" t="n">
-        <v>3.52838845420191</v>
+        <v>0.1955868755329219</v>
       </c>
       <c r="V16" t="n">
-        <v>4.042282681302865</v>
+        <v>0.2264303132993828</v>
       </c>
       <c r="W16" t="n">
-        <v>4.55617690840382</v>
+        <v>0.2572737510658438</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -2658,22 +2662,22 @@
         <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.06623456498083899</v>
+        <v>0.04354452427606749</v>
       </c>
       <c r="AA16" t="n">
-        <v>8556.1890406</v>
+        <v>63442.537944</v>
       </c>
       <c r="AB16" t="n">
-        <v>1143.6534084</v>
+        <v>75265.604096</v>
       </c>
       <c r="AC16" t="n">
-        <v>120.344229</v>
+        <v>9.207787</v>
       </c>
       <c r="AD16" t="n">
-        <v>284.259438</v>
+        <v>13.45676</v>
       </c>
       <c r="AE16" t="n">
-        <v>51797630.96606171</v>
+        <v>515137839.5663076</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2688,12 +2692,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BERAUSDT</t>
+          <t>RIVERUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berachain</t>
+          <t>River</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2703,24 +2707,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>58.488</v>
+        <v>61.2</v>
       </c>
       <c r="I17" t="n">
-        <v>73.11</v>
+        <v>68</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2740,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5956938493948337</v>
+        <v>22.12559818078699</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6808</v>
+        <v>22.813</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.28689429840944</v>
+        <v>3.106816880593621</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2754,19 +2758,19 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.3345</v>
+        <v>19.37185462074383</v>
       </c>
       <c r="T17" t="n">
-        <v>43.84699450232379</v>
+        <v>12.44596208221122</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8568876987896674</v>
+        <v>24.87934174083016</v>
       </c>
       <c r="V17" t="n">
-        <v>1.118081548184501</v>
+        <v>27.63308530087333</v>
       </c>
       <c r="W17" t="n">
-        <v>1.379275397579335</v>
+        <v>30.38682886091649</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -2775,22 +2779,22 @@
         <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.07329766180459663</v>
+        <v>0.03197596108569667</v>
       </c>
       <c r="AA17" t="n">
-        <v>4767.34081</v>
+        <v>18459.893822</v>
       </c>
       <c r="AB17" t="n">
-        <v>3411.898634</v>
+        <v>14274.476715</v>
       </c>
       <c r="AC17" t="n">
-        <v>83.56501900000001</v>
+        <v>15.914365</v>
       </c>
       <c r="AD17" t="n">
-        <v>151.699058</v>
+        <v>86.473321</v>
       </c>
       <c r="AE17" t="n">
-        <v>155710072.9150086</v>
+        <v>444714621.9859819</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2805,12 +2809,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2820,29 +2824,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_chased</t>
+          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>58.36</v>
+        <v>59.76</v>
       </c>
       <c r="I18" t="n">
-        <v>72.95</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>rebound_not_confirmed</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>direct</t>
@@ -2857,13 +2865,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.858684910420141</v>
+        <v>9.857178226551421</v>
       </c>
       <c r="P18" t="n">
-        <v>4.055</v>
+        <v>10.164</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.087616484303292</v>
+        <v>3.112673489276263</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2871,19 +2879,19 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>2.848</v>
+        <v>9.63603747562024</v>
       </c>
       <c r="T18" t="n">
-        <v>26.19247059252878</v>
+        <v>2.24344884355964</v>
       </c>
       <c r="U18" t="n">
-        <v>4.869369820840282</v>
+        <v>10.0783189774826</v>
       </c>
       <c r="V18" t="n">
-        <v>5.880054731260422</v>
+        <v>10.29945972841378</v>
       </c>
       <c r="W18" t="n">
-        <v>6.890739641680564</v>
+        <v>10.52060047934496</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -2892,22 +2900,22 @@
         <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0246396451891175</v>
+        <v>0.02949997541668828</v>
       </c>
       <c r="AA18" t="n">
-        <v>124643.61361</v>
+        <v>584956.99023</v>
       </c>
       <c r="AB18" t="n">
-        <v>143398.26408</v>
+        <v>628198.02321</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.553392</v>
+        <v>1.474999</v>
       </c>
       <c r="AD18" t="n">
-        <v>8.723209000000001</v>
+        <v>1.474999</v>
       </c>
       <c r="AE18" t="n">
-        <v>2571024503.828282</v>
+        <v>4395247051.317751</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2922,12 +2930,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>BERAUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Berachain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2937,7 +2945,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2951,40 +2959,36 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>56.816</v>
+        <v>58.488</v>
       </c>
       <c r="I19" t="n">
-        <v>71.02</v>
+        <v>73.11</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2677985231082082</v>
+        <v>0.5956938493948337</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2875</v>
+        <v>0.657</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.35682805981388</v>
+        <v>10.29155339902323</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2992,19 +2996,19 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.2208</v>
+        <v>0.3345</v>
       </c>
       <c r="T19" t="n">
-        <v>17.54995605006294</v>
+        <v>43.84699450232379</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3147970462164164</v>
+        <v>0.8568876987896674</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3617955693246245</v>
+        <v>1.118081548184501</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4087940924328327</v>
+        <v>1.379275397579335</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -3013,22 +3017,22 @@
         <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.03474031613687302</v>
+        <v>0.07605141075366111</v>
       </c>
       <c r="AA19" t="n">
-        <v>793052.802506</v>
+        <v>4671.892378</v>
       </c>
       <c r="AB19" t="n">
-        <v>854570.910666</v>
+        <v>4350.954513</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.737016</v>
+        <v>60.274921</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.692697</v>
+        <v>155.101459</v>
       </c>
       <c r="AE19" t="n">
-        <v>10351544533.11743</v>
+        <v>150245816.3580998</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3043,12 +3047,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATHUSDT</t>
+          <t>PENGUUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aethir</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3072,10 +3076,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>56.68</v>
+        <v>57.072</v>
       </c>
       <c r="I20" t="n">
-        <v>70.84999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -3099,13 +3103,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00604660004796421</v>
+        <v>0.007069091220954474</v>
       </c>
       <c r="P20" t="n">
-        <v>0.00645</v>
+        <v>0.007894</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.671517031651675</v>
+        <v>11.66923375667157</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3113,19 +3117,19 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.004808</v>
+        <v>0.005287</v>
       </c>
       <c r="T20" t="n">
-        <v>20.48423970725873</v>
+        <v>25.20962264105363</v>
       </c>
       <c r="U20" t="n">
-        <v>0.00728520009592842</v>
+        <v>0.008851182441908948</v>
       </c>
       <c r="V20" t="n">
-        <v>0.00852380014389263</v>
+        <v>0.01063327366286342</v>
       </c>
       <c r="W20" t="n">
-        <v>0.00976240019185684</v>
+        <v>0.0124153648838179</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -3134,22 +3138,22 @@
         <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1705294163243117</v>
+        <v>0.02531004808909473</v>
       </c>
       <c r="AA20" t="n">
-        <v>5324.76798743</v>
+        <v>29276.34004582</v>
       </c>
       <c r="AB20" t="n">
-        <v>5029.66374253</v>
+        <v>19620.14897968</v>
       </c>
       <c r="AC20" t="n">
-        <v>42.057617</v>
+        <v>12.396352</v>
       </c>
       <c r="AD20" t="n">
-        <v>2068.983683</v>
+        <v>42.111005</v>
       </c>
       <c r="AE20" t="n">
-        <v>117710258.9225873</v>
+        <v>496144842.9709927</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3164,12 +3168,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>MOODENGUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Moo Deng (moodengsol.com)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3179,7 +3183,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3193,10 +3197,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>55.688</v>
+        <v>56.584</v>
       </c>
       <c r="I21" t="n">
-        <v>69.61</v>
+        <v>70.73</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -3208,25 +3212,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9.018915284177879</v>
+        <v>0.05128893610481111</v>
       </c>
       <c r="P21" t="n">
-        <v>9.753</v>
+        <v>0.05631</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.139390300183269</v>
+        <v>9.789760280712656</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3234,43 +3238,43 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>7.16</v>
+        <v>0.038</v>
       </c>
       <c r="T21" t="n">
-        <v>20.61129554503104</v>
+        <v>25.90994688923671</v>
       </c>
       <c r="U21" t="n">
-        <v>10.87783056835576</v>
+        <v>0.06457787220962222</v>
       </c>
       <c r="V21" t="n">
-        <v>12.73674585253364</v>
+        <v>0.07786680831443334</v>
       </c>
       <c r="W21" t="n">
-        <v>14.59566113671152</v>
+        <v>0.09115574441924446</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="Y21" t="n">
         <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.02050020500203866</v>
+        <v>0.08873901854645741</v>
       </c>
       <c r="AA21" t="n">
-        <v>1301598.70394</v>
+        <v>13201.1114988</v>
       </c>
       <c r="AB21" t="n">
-        <v>1033089.37253</v>
+        <v>5122.6501506</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.841624</v>
+        <v>29.162257</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.785407</v>
+        <v>2034.637063</v>
       </c>
       <c r="AE21" t="n">
-        <v>6902901100.43938</v>
+        <v>55773153.95388348</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3508,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3719,12 +3723,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NEOUSDT</t>
+          <t>CAKEUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3734,7 +3738,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_chased</t>
+          <t>effective_rr_insufficient | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3748,10 +3752,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>75.288</v>
+        <v>75.904</v>
       </c>
       <c r="I2" t="n">
-        <v>94.11</v>
+        <v>94.88</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -3759,25 +3763,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.645300510556884</v>
+        <v>1.377583526080592</v>
       </c>
       <c r="P2" t="n">
-        <v>2.848</v>
+        <v>1.502</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.662626179301046</v>
+        <v>9.031501289318467</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -3785,19 +3789,19 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>2.419</v>
+        <v>1.169</v>
       </c>
       <c r="T2" t="n">
-        <v>8.55481294672429</v>
+        <v>15.14126164632936</v>
       </c>
       <c r="U2" t="n">
-        <v>2.871601021113768</v>
+        <v>1.586167052161185</v>
       </c>
       <c r="V2" t="n">
-        <v>3.097901531670652</v>
+        <v>1.794750578241777</v>
       </c>
       <c r="W2" t="n">
-        <v>3.324202042227536</v>
+        <v>2.00333410432237</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -3806,22 +3810,22 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03509387611861343</v>
+        <v>0.06655574043260498</v>
       </c>
       <c r="AA2" t="n">
-        <v>12338.509143</v>
+        <v>129519.55706</v>
       </c>
       <c r="AB2" t="n">
-        <v>13356.687751</v>
+        <v>101197.76054</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.643408</v>
+        <v>4.305977</v>
       </c>
       <c r="AD2" t="n">
-        <v>79.62982700000001</v>
+        <v>10.721407</v>
       </c>
       <c r="AE2" t="n">
-        <v>200342902.5119538</v>
+        <v>494925978.2526067</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -3836,12 +3840,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUSDT</t>
+          <t>NEOUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3851,7 +3855,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3865,19 +3869,15 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.488</v>
+        <v>75.288</v>
       </c>
       <c r="I3" t="n">
-        <v>81.86</v>
+        <v>94.11</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>none</t>
@@ -3892,13 +3892,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04251637342558565</v>
+        <v>2.645300510556884</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04894</v>
+        <v>2.789</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.10859477621558</v>
+        <v>5.432255763367499</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.03667</v>
+        <v>2.419</v>
       </c>
       <c r="T3" t="n">
-        <v>13.7508751441801</v>
+        <v>8.55481294672429</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04836274685117131</v>
+        <v>2.871601021113768</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05420912027675696</v>
+        <v>3.097901531670652</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06005549370234261</v>
+        <v>3.324202042227536</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -3927,22 +3927,22 @@
         <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02039775624680494</v>
+        <v>0.07165890361876674</v>
       </c>
       <c r="AA3" t="n">
-        <v>14639.4710375</v>
+        <v>12512.478873</v>
       </c>
       <c r="AB3" t="n">
-        <v>16992.6016453</v>
+        <v>11025.137397</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.539845</v>
+        <v>17.784624</v>
       </c>
       <c r="AD3" t="n">
-        <v>44.599143</v>
+        <v>99.703883</v>
       </c>
       <c r="AE3" t="n">
-        <v>141556508.4303511</v>
+        <v>196330253.5828413</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EIGENUSDT</t>
+          <t>BBUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EigenCloud</t>
+          <t>BounceBit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>65.47199999999999</v>
+        <v>67.592</v>
       </c>
       <c r="I4" t="n">
-        <v>81.84</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -4001,25 +4001,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1935899444960997</v>
+        <v>0.02790929470802848</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2196</v>
+        <v>0.02884</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.43564386652545</v>
+        <v>3.334750310633217</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4027,43 +4027,43 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.1696</v>
+        <v>0.0235</v>
       </c>
       <c r="T4" t="n">
-        <v>12.39214389907687</v>
+        <v>15.79866046116919</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2175798889921995</v>
+        <v>0.03231858941605696</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2415698334882992</v>
+        <v>0.03672788412408544</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2655597779843989</v>
+        <v>0.04113717883211392</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.999999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09103322712790429</v>
+        <v>0.1731601731601661</v>
       </c>
       <c r="AA4" t="n">
-        <v>81765.935514</v>
+        <v>518.2395081999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>53725.338742</v>
+        <v>10856.6918679</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.599563</v>
+        <v>12.120301</v>
       </c>
       <c r="AD4" t="n">
-        <v>33.968546</v>
+        <v>126.795303</v>
       </c>
       <c r="AE4" t="n">
-        <v>141862203.1409119</v>
+        <v>30100401.45894412</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ONTUSDT</t>
+          <t>SUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>61.512</v>
+        <v>65.488</v>
       </c>
       <c r="I5" t="n">
-        <v>76.89</v>
+        <v>81.86</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -4134,13 +4134,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04230336070690488</v>
+        <v>0.04251637342558565</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0436</v>
+        <v>0.04999</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.065097598459787</v>
+        <v>17.57823156646949</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4148,19 +4148,19 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.03883</v>
+        <v>0.03667</v>
       </c>
       <c r="T5" t="n">
-        <v>8.210602299353358</v>
+        <v>13.7508751441801</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04577672141380976</v>
+        <v>0.04836274685117131</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04925008212071463</v>
+        <v>0.05420912027675696</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05272344282761951</v>
+        <v>0.06005549370234261</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -4169,22 +4169,22 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1375200550080164</v>
+        <v>0.01999800019997225</v>
       </c>
       <c r="AA5" t="n">
-        <v>4756.5967106</v>
+        <v>15857.7854915</v>
       </c>
       <c r="AB5" t="n">
-        <v>3056.9484425</v>
+        <v>12320.2825642</v>
       </c>
       <c r="AC5" t="n">
-        <v>81.090335</v>
+        <v>15.202372</v>
       </c>
       <c r="AD5" t="n">
-        <v>8743.020782</v>
+        <v>284.805279</v>
       </c>
       <c r="AE5" t="n">
-        <v>40774760.97905913</v>
+        <v>143834978.4251222</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REZUSDT</t>
+          <t>EIGENUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Renzo</t>
+          <t>EigenCloud</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4214,50 +4214,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | btc_regime_caution | entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.2</v>
+        <v>65.47199999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>68</v>
+        <v>81.84</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003521820873396659</v>
+        <v>0.1935899444960997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.004027</v>
+        <v>0.2152</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.34425953969984</v>
+        <v>11.16279854315245</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4265,19 +4269,19 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.00334433672338398</v>
+        <v>0.1696</v>
       </c>
       <c r="T6" t="n">
-        <v>5.039556422456634</v>
+        <v>12.39214389907687</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003699305023409339</v>
+        <v>0.2175798889921995</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003876789173422019</v>
+        <v>0.2415698334882992</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004054273323434698</v>
+        <v>0.2655597779843989</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -4286,22 +4290,22 @@
         <v>2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.198461920119082</v>
+        <v>0.09280742459397016</v>
       </c>
       <c r="AA6" t="n">
-        <v>10157.08912587</v>
+        <v>58986.53928599999</v>
       </c>
       <c r="AB6" t="n">
-        <v>2226.29849701</v>
+        <v>56898.246609</v>
       </c>
       <c r="AC6" t="n">
-        <v>82.28304300000001</v>
+        <v>21.230981</v>
       </c>
       <c r="AD6" t="n">
-        <v>190.330867</v>
+        <v>22.835401</v>
       </c>
       <c r="AE6" t="n">
-        <v>28484778.8716311</v>
+        <v>139189718.4834139</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -4316,12 +4320,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZENUSDT</t>
+          <t>BONKUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Horizen</t>
+          <t>Bonk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4345,10 +4349,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>59.168</v>
+        <v>61.016</v>
       </c>
       <c r="I7" t="n">
-        <v>73.95999999999999</v>
+        <v>76.27</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -4372,13 +4376,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.653305171976704</v>
+        <v>6.061063817434262e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>6.248</v>
+        <v>6.517e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.5194184628699</v>
+        <v>7.522378847988143</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -4386,43 +4390,43 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4.94</v>
+        <v>5.135e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>12.61748924350555</v>
+        <v>15.27889897431039</v>
       </c>
       <c r="U7" t="n">
-        <v>6.366610343953407</v>
+        <v>6.987127634868524e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>7.07991551593011</v>
+        <v>7.913191452302786e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.793220687906813</v>
+        <v>8.839255269737048e-06</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04799616030717724</v>
+        <v>0.1532332209623032</v>
       </c>
       <c r="AA7" t="n">
-        <v>14692.91218</v>
+        <v>189815.638465952</v>
       </c>
       <c r="AB7" t="n">
-        <v>14193.57388</v>
+        <v>211253.737924424</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.417535</v>
+        <v>7.661661</v>
       </c>
       <c r="AD7" t="n">
-        <v>107.110515</v>
+        <v>7.661661</v>
       </c>
       <c r="AE7" t="n">
-        <v>111479311.0662243</v>
+        <v>574448583.7315314</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -4437,12 +4441,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RENDERUSDT</t>
+          <t>ETCUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4452,29 +4456,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>entry_chased</t>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>55.44</v>
+        <v>59.976</v>
       </c>
       <c r="I8" t="n">
-        <v>61.6</v>
+        <v>74.97</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>direct</t>
@@ -4489,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.794923351021833</v>
+        <v>8.460252391107007</v>
       </c>
       <c r="P8" t="n">
-        <v>1.884</v>
+        <v>8.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.962699322366948</v>
+        <v>5.552406561614731</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -4503,43 +4511,43 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1.658853690195508</v>
+        <v>7.14</v>
       </c>
       <c r="T8" t="n">
-        <v>7.580806208179395</v>
+        <v>15.60535466406168</v>
       </c>
       <c r="U8" t="n">
-        <v>1.930993011848158</v>
+        <v>9.780504782214013</v>
       </c>
       <c r="V8" t="n">
-        <v>2.067062672674483</v>
+        <v>11.10075717332102</v>
       </c>
       <c r="W8" t="n">
-        <v>2.203132333500808</v>
+        <v>12.42100956442803</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05303632988596605</v>
+        <v>0.1119194180190239</v>
       </c>
       <c r="AA8" t="n">
-        <v>147861.81799</v>
+        <v>88378.84323</v>
       </c>
       <c r="AB8" t="n">
-        <v>153210.54343</v>
+        <v>55029.01777</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.80983</v>
+        <v>5.595971</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.509838</v>
+        <v>10.748068</v>
       </c>
       <c r="AE8" t="n">
-        <v>976872435.750208</v>
+        <v>1391286098.117296</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -4548,8 +4556,726 @@
       </c>
       <c r="AG8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KASUSDT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kaspa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59.392</v>
+      </c>
+      <c r="I9" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03061209080528285</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.03369</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.05455398095834</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0.025188</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17.71878582153819</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.03603618161056571</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.04146027241584856</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04688436322113142</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.999999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.08301707779886221</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>52430.40961702</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>34047.04133134</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.503122</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>20.501842</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>917032545.5770435</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ZENUSDT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Horizen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59.168</v>
+      </c>
+      <c r="I10" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.653305171976704</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.214</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9.918000372643032</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12.61748924350555</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6.366610343953407</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.07991551593011</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7.793220687906813</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.03218020917135607</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>14449.31822</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12521.60339</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.525416999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>105.23279</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>111086132.4720163</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QUBICUSDT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Qubic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_chased</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pullback_to_ema</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="I11" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9.010145353508996e-07</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.0371e-06</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>15.10358149728428</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>8.043787136442057e-07</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10.72522339154709</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9.976503570575936e-07</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.094286178764287e-06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.190922000470982e-06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.999999999999999</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.211905220574066</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2460.5571155293</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3172.491420091</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>107.98297</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>505.602041</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>140670440.2592961</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TAOUSDT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bittensor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>entry_chased</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pullback_to_ema</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>256.7971756600807</v>
+      </c>
+      <c r="P12" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12.9295909328339</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>230.3411380137109</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10.3023086520972</v>
+      </c>
+      <c r="U12" t="n">
+        <v>283.2532133064504</v>
+      </c>
+      <c r="V12" t="n">
+        <v>309.7092509528201</v>
+      </c>
+      <c r="W12" t="n">
+        <v>336.1652885991899</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.04821932906249335</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>166264.25511</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>183500.17237</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.410966</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.392047</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3121809476.65737</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FARTCOINUSDT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fartcoin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tradeability_marginal | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>58.032</v>
+      </c>
+      <c r="I13" t="n">
+        <v>72.54000000000001</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1634675277966182</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.18023</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10.2543131527854</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0.13836</v>
+      </c>
+      <c r="T13" t="n">
+        <v>15.35933658203746</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1885750555932365</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2136825833898547</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.2387901111864729</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1883552157775231</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8207.1954768</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7865.687407400001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>38.02951</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>305.197508</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>179907225.1536074</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ORDIUSDT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ORDI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>reversal_base_reclaim</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>57.648</v>
+      </c>
+      <c r="I14" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DIRECT_OK</t>
+        </is>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.527602926075091</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.939265345655743</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>chased</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>2.181</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13.71271264562517</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.874205852150181</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.220808778225272</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.567411704300363</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.07396449704142841</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>49739.07573</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>48814.61005</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.821902</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>16.473303</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>56859550.32031852</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>RISK_OFF</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG8"/>
+  <autoFilter ref="A1:AG14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>